--- a/408/OS/2024/ModularAutomation/reports/template_pc.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/template_pc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>启机次数</t>
   </si>
@@ -123,6 +123,12 @@
     <t>DMESG日志</t>
   </si>
   <si>
+    <t>开始时间</t>
+  </si>
+  <si>
+    <t>结束时间</t>
+  </si>
+  <si>
     <t>#END_OF_ROW</t>
   </si>
   <si>
@@ -582,6 +588,12 @@
   </si>
   <si>
     <t>#dmesg_log↓</t>
+  </si>
+  <si>
+    <t>#start_time↓</t>
+  </si>
+  <si>
+    <t>#end_time↓</t>
   </si>
   <si>
     <t>#END_OF_COL</t>
@@ -597,14 +609,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1077,150 +1082,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1534,7 +1542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="15.2222222222222" style="1" customWidth="1"/>
@@ -1556,12 +1564,14 @@
     <col min="22" max="22" width="23.1111111111111" style="1" customWidth="1"/>
     <col min="23" max="23" width="21.5555555555556" style="1" customWidth="1"/>
     <col min="24" max="24" width="20.8888888888889" style="1" customWidth="1"/>
-    <col min="25" max="25" width="50.7777777777778" style="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="1"/>
+    <col min="25" max="25" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="26" max="26" width="15.2222222222222" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:28">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1640,165 +1650,183 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:28">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
